--- a/capstone-docs/meeting_minutes/Meeting minutes of company.xlsx
+++ b/capstone-docs/meeting_minutes/Meeting minutes of company.xlsx
@@ -35,7 +35,7 @@
     <t>MEETING MINUTES OF COMPANY — IELTSPath — TUẦN 1</t>
   </si>
   <si>
-    <t>Thời gian tuần: 07/09/2026 – 13/09/2026  ·  Thành phần: Đại diện IELTS Space; nhóm: Hiếu, Sơn, Phú, Hoàng</t>
+    <t>Thời gian tuần: 07/09/2026 – 13/09/2026  ·  Thành phần: Đại diện IELTS Space; nhóm: Hiếu, Sơn, Phú, Hoàng, Tùng</t>
   </si>
   <si>
     <t>Buổi 1 — Thứ Ba, 08/09/2026 · Google Meet · Nhận đặt hàng và yêu cầu ban đầu</t>
@@ -65,7 +65,7 @@
     <t>MEETING MINUTES OF COMPANY — IELTSPath — TUẦN 2</t>
   </si>
   <si>
-    <t>Thời gian tuần: 14/09/2026 – 20/09/2026  ·  Thành phần: Đại diện IELTS Space; nhóm: Hiếu, Sơn, Phú, Hoàng</t>
+    <t>Thời gian tuần: 14/09/2026 – 20/09/2026  ·  Thành phần: Đại diện IELTS Space; nhóm: Hiếu, Sơn, Phú, Hoàng, Tùng</t>
   </si>
   <si>
     <t>Buổi 2 — Thứ Ba, 15/09/2026 · Google Meet · Góp ý Vision &amp; Scope</t>
@@ -80,7 +80,7 @@
     <t>Trung tâm xác nhận các vai trò: học viên, người soạn nội dung, giám khảo chấm bài, đội sales cấp thẻ kích hoạt, quản trị viên.</t>
   </si>
   <si>
-    <t>Thống nhất luồng thẻ kích hoạt: admin tạo lô thẻ theo gói, sales giao thẻ cho học viên, hệ thống ghi lại ai kích hoạt thẻ và khi nào.</t>
+    <t>Thống nhất luồng thẻ kích hoạt: sales tạo lô thẻ theo gói và giao thẻ cho học viên, admin quản lý gói, hệ thống ghi lại ai kích hoạt thẻ và khi nào.</t>
   </si>
   <si>
     <t>Việc tiếp theo: nhóm chỉnh Vision &amp; Scope theo góp ý và bắt đầu SRS.</t>
@@ -92,7 +92,7 @@
     <t>MEETING MINUTES OF COMPANY — IELTSPath — TUẦN 3</t>
   </si>
   <si>
-    <t>Thời gian tuần: 21/09/2026 – 27/09/2026  ·  Thành phần: Đại diện IELTS Space; nhóm: Hiếu, Sơn, Phú, Hoàng</t>
+    <t>Thời gian tuần: 21/09/2026 – 27/09/2026  ·  Thành phần: Đại diện IELTS Space; nhóm: Hiếu, Sơn, Phú, Hoàng, Tùng</t>
   </si>
   <si>
     <t>Buổi 3 — Thứ Ba, 22/09/2026 · Google Meet · Luồng học và quy tắc nội dung</t>
@@ -119,7 +119,7 @@
     <t>MEETING MINUTES OF COMPANY — IELTSPath — TUẦN 4</t>
   </si>
   <si>
-    <t>Thời gian tuần: 28/09/2026 – 04/10/2026  ·  Thành phần: Đại diện IELTS Space; nhóm: Hiếu, Sơn, Phú, Hoàng</t>
+    <t>Thời gian tuần: 28/09/2026 – 04/10/2026  ·  Thành phần: Đại diện IELTS Space; nhóm: Hiếu, Sơn, Phú, Hoàng, Tùng</t>
   </si>
   <si>
     <t>Buổi 4 — Thứ Ba, 29/09/2026 · Google Meet · Demo prototype, chấm Writing</t>
@@ -146,7 +146,7 @@
     <t>MEETING MINUTES OF COMPANY — IELTSPath — TUẦN 5</t>
   </si>
   <si>
-    <t>Thời gian tuần: 05/10/2026 – 11/10/2026  ·  Thành phần: Đại diện IELTS Space; nhóm: Hiếu, Sơn, Phú, Hoàng</t>
+    <t>Thời gian tuần: 05/10/2026 – 11/10/2026  ·  Thành phần: Đại diện IELTS Space; nhóm: Hiếu, Sơn, Phú, Hoàng, Tùng</t>
   </si>
   <si>
     <t>Buổi 5 — Thứ Năm, 08/10/2026 · Google Meet · Demo luồng chính, khóa học theo band</t>
